--- a/WP-2/Data_cleaning/old_excel/ADNI_variables_statistics2.xlsx
+++ b/WP-2/Data_cleaning/old_excel/ADNI_variables_statistics2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifabfoundation-my.sharepoint.com/personal/chiara_pollicini_ifabfoundation_org/Documents/Documenti/Github/AIND/WP-2/Data_cleaning/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifabfoundation-my.sharepoint.com/personal/chiara_pollicini_ifabfoundation_org/Documents/Documenti/Github/AIND/WP-2/Data_cleaning/old_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="11_AD4D5CB4E552A5DACE1C640E809867505BDEDD88" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4175D2B-F1E7-4B17-8131-247C77DDEDFE}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="11_AD4D5CB4E552A5DACE1C640E809867505BDEDD88" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10CB9785-463C-4B76-B0AE-A2345F2801D7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="Foglio2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1423,26 +1422,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1451,51 +1448,6 @@
     <cellStyle name="Valore valido" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="15">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1695,10 +1647,55 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
       <border outline="0">
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -1714,28 +1711,24 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CC5D438-3046-4DC5-AB06-3296B8262536}" name="Tabella1" displayName="Tabella1" ref="A1:K300" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="14" tableBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CC5D438-3046-4DC5-AB06-3296B8262536}" name="Tabella1" displayName="Tabella1" ref="A1:K300" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11">
   <autoFilter ref="A1:K300" xr:uid="{1CC5D438-3046-4DC5-AB06-3296B8262536}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K300">
     <sortCondition ref="A1:A300"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{C64A19B9-CF21-4F20-977B-9D74C661F7DE}" name="file_name" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{8BD8A82D-8311-44B0-9E19-FEF598652BDB}" name="file_code" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{8CACF3B8-E302-4CA6-B9E4-432CC91AC8EC}" name="parameter" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{E60C278F-CBEE-4184-9152-98C33BEE1123}" name="variable_code" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{BE674D72-08D6-4039-922F-C0E923816AAB}" name="type_variable" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{158781C7-CB92-4F57-9A35-FA4E8EFE021D}" name="classes" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{8C01ECA9-19A3-46F2-8450-15ECBF0BD759}" name="range" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{2257884A-3053-42CB-8DB7-5A261A5590CD}" name="valid_values" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{16080A17-C0C3-4AC1-A096-C031E2085069}" name="missing_values" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{4A089D96-451F-4A86-895C-69CA2130B5FD}" name="missing_pop" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{7823E1E7-1801-45D7-8ABA-671085EF56BB}" name="del" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{C64A19B9-CF21-4F20-977B-9D74C661F7DE}" name="file_name" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{8BD8A82D-8311-44B0-9E19-FEF598652BDB}" name="file_code" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{8CACF3B8-E302-4CA6-B9E4-432CC91AC8EC}" name="parameter" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{E60C278F-CBEE-4184-9152-98C33BEE1123}" name="variable_code" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{BE674D72-08D6-4039-922F-C0E923816AAB}" name="type_variable" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{158781C7-CB92-4F57-9A35-FA4E8EFE021D}" name="classes" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{8C01ECA9-19A3-46F2-8450-15ECBF0BD759}" name="range" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{2257884A-3053-42CB-8DB7-5A261A5590CD}" name="valid_values" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{16080A17-C0C3-4AC1-A096-C031E2085069}" name="missing_values" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{4A089D96-451F-4A86-895C-69CA2130B5FD}" name="missing_pop" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{7823E1E7-1801-45D7-8ABA-671085EF56BB}" name="del" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2007,16 +2000,14 @@
   <dimension ref="A1:K300"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="108.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11" style="4" customWidth="1"/>
-    <col min="3" max="3" width="12" style="4" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31" style="4" customWidth="1"/>
-    <col min="6" max="7" width="8.88671875" style="4"/>
-    <col min="8" max="8" width="13.6640625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="13.77734375" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="4"/>
+    <col min="1" max="1" width="108.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -2321,3668 +2312,3668 @@
       <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D16" s="6" t="s">
+      <c r="C16" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" t="s">
         <v>117</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" t="s">
         <v>117</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" t="s">
         <v>100</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" t="s">
         <v>429</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D21" s="8" t="s">
+      <c r="C21" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="5" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" t="s">
         <v>429</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D22" s="8" t="s">
+      <c r="C22" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="5" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" t="s">
         <v>429</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D23" s="8" t="s">
+      <c r="C23" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="5" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" t="s">
         <v>429</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D24" s="8" t="s">
+      <c r="C24" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" t="s">
         <v>429</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D25" s="8" t="s">
+      <c r="C25" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="5" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" t="s">
         <v>429</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D26" s="8" t="s">
+      <c r="C26" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="5" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" t="s">
         <v>429</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D27" s="8" t="s">
+      <c r="C27" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="5" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" t="s">
         <v>429</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D28" s="8" t="s">
+      <c r="C28" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D28" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="5" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" t="s">
         <v>429</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D29" s="8" t="s">
+      <c r="C29" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="5" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" t="s">
         <v>429</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D30" s="8" t="s">
+      <c r="C30" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" t="s">
         <v>85</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" t="s">
         <v>85</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" t="s">
         <v>85</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" t="s">
         <v>85</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" t="s">
         <v>85</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" t="s">
         <v>85</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" t="s">
         <v>85</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" t="s">
         <v>85</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" t="s">
         <v>85</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" t="s">
         <v>85</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" t="s">
         <v>85</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" t="s">
         <v>85</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" t="s">
         <v>85</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D45" s="6" t="s">
+      <c r="C45" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="5" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D46" s="6" t="s">
+      <c r="C46" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D46" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="5" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C47" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D47" s="6" t="s">
+      <c r="C47" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D47" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="5" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D48" s="6" t="s">
+      <c r="C48" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D48" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E48" s="5" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C49" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D49" s="6" t="s">
+      <c r="C49" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D49" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E49" s="6" t="s">
+      <c r="E49" s="5" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D50" s="6" t="s">
+      <c r="C50" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D50" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="E50" s="5" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D51" s="6" t="s">
+      <c r="C51" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D51" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="E51" s="5" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="7" t="s">
+      <c r="A52" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D52" s="6" t="s">
+      <c r="C52" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D52" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="E52" s="5" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D53" s="6" t="s">
+      <c r="C53" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D53" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E53" s="5" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D54" s="6" t="s">
+      <c r="C54" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D54" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="E54" s="5" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D55" s="6" t="s">
+      <c r="C55" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D55" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="E55" s="5" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D56" s="6" t="s">
+      <c r="C56" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D56" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E56" s="6" t="s">
+      <c r="E56" s="5" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C57" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D57" s="6" t="s">
+      <c r="C57" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D57" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="E57" s="6" t="s">
+      <c r="E57" s="5" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D58" s="6" t="s">
+      <c r="C58" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D58" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="E58" s="6" t="s">
+      <c r="E58" s="5" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="7" t="s">
+      <c r="A59" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D59" s="6" t="s">
+      <c r="C59" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D59" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="E59" s="6" t="s">
+      <c r="E59" s="5" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C60" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D60" s="6" t="s">
+      <c r="C60" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D60" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="E60" s="6" t="s">
+      <c r="E60" s="5" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C61" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D61" s="6" t="s">
+      <c r="C61" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D61" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="E61" s="6" t="s">
+      <c r="E61" s="5" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C62" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D62" s="6" t="s">
+      <c r="C62" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D62" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="E62" s="6" t="s">
+      <c r="E62" s="5" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A63" s="7" t="s">
+      <c r="A63" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C63" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D63" s="6" t="s">
+      <c r="C63" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D63" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="E63" s="6" t="s">
+      <c r="E63" s="5" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C64" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D64" s="6" t="s">
+      <c r="C64" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D64" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="E64" s="6" t="s">
+      <c r="E64" s="5" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A65" s="7" t="s">
+      <c r="A65" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C65" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D65" s="6" t="s">
+      <c r="C65" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D65" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="E65" s="6" t="s">
+      <c r="E65" s="5" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A66" s="7" t="s">
+      <c r="A66" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C66" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D66" s="6" t="s">
+      <c r="C66" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D66" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E66" s="6" t="s">
+      <c r="E66" s="5" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A67" s="7" t="s">
+      <c r="A67" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C67" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D67" s="6" t="s">
+      <c r="C67" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D67" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="E67" s="6" t="s">
+      <c r="E67" s="5" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="7" t="s">
+      <c r="A68" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" t="s">
         <v>117</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="7" t="s">
+      <c r="A69" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" t="s">
         <v>108</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="7" t="s">
+      <c r="A70" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" t="s">
         <v>108</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="7" t="s">
+      <c r="A71" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" t="s">
         <v>108</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D71" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="7" t="s">
+      <c r="A72" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" t="s">
         <v>117</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D72" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="7" t="s">
+      <c r="A73" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C73" t="s">
         <v>108</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="D73" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="7" t="s">
+      <c r="A74" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D74" s="4" t="s">
+      <c r="C74" t="s">
+        <v>12</v>
+      </c>
+      <c r="D74" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="7" t="s">
+      <c r="A75" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C75" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D75" s="4" t="s">
+      <c r="C75" t="s">
+        <v>12</v>
+      </c>
+      <c r="D75" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C76" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D76" s="4" t="s">
+      <c r="C76" t="s">
+        <v>12</v>
+      </c>
+      <c r="D76" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="7" t="s">
+      <c r="A77" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" t="s">
         <v>117</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="D77" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="7" t="s">
+      <c r="A78" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" t="s">
         <v>117</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D78" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="7" t="s">
+      <c r="A79" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" t="s">
         <v>117</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="D79" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="7" t="s">
+      <c r="A80" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="C80" s="6" t="s">
+      <c r="C80" s="5" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="7" t="s">
+      <c r="A81" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="C81" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D81" s="6" t="s">
+      <c r="C81" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D81" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="E81" s="6" t="s">
+      <c r="E81" s="5" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" s="7" t="s">
+      <c r="A82" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C82" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D82" s="6" t="s">
+      <c r="C82" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D82" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="E82" s="6" t="s">
+      <c r="E82" s="5" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" s="7" t="s">
+      <c r="A83" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="C83" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D83" s="6" t="s">
+      <c r="C83" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D83" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="E83" s="6" t="s">
+      <c r="E83" s="5" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" s="7" t="s">
+      <c r="A84" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="C84" t="s">
         <v>100</v>
       </c>
-      <c r="D84" s="4" t="s">
+      <c r="D84" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="7" t="s">
+      <c r="A85" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" t="s">
         <v>100</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="D85" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" s="7" t="s">
+      <c r="A86" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C86" t="s">
         <v>100</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D86" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" s="7" t="s">
+      <c r="A87" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D87" s="4" t="s">
+      <c r="C87" t="s">
+        <v>12</v>
+      </c>
+      <c r="D87" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="7" t="s">
+      <c r="A88" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C88" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D88" s="4" t="s">
+      <c r="C88" t="s">
+        <v>12</v>
+      </c>
+      <c r="D88" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" s="7" t="s">
+      <c r="A89" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C89" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D89" s="4" t="s">
+      <c r="C89" t="s">
+        <v>12</v>
+      </c>
+      <c r="D89" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90" s="7" t="s">
+      <c r="A90" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C90" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D90" s="4" t="s">
+      <c r="C90" t="s">
+        <v>12</v>
+      </c>
+      <c r="D90" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C91" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D91" s="4" t="s">
+      <c r="C91" t="s">
+        <v>12</v>
+      </c>
+      <c r="D91" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="7" t="s">
+      <c r="A92" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C92" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D92" s="4" t="s">
+      <c r="C92" t="s">
+        <v>12</v>
+      </c>
+      <c r="D92" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="7" t="s">
+      <c r="A93" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C93" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D93" s="4" t="s">
+      <c r="C93" t="s">
+        <v>12</v>
+      </c>
+      <c r="D93" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="7" t="s">
+      <c r="A94" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C94" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D94" s="4" t="s">
+      <c r="C94" t="s">
+        <v>12</v>
+      </c>
+      <c r="D94" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="7" t="s">
+      <c r="A95" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C95" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D95" s="4" t="s">
+      <c r="C95" t="s">
+        <v>12</v>
+      </c>
+      <c r="D95" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" s="7" t="s">
+      <c r="A96" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C96" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D96" s="4" t="s">
+      <c r="C96" t="s">
+        <v>12</v>
+      </c>
+      <c r="D96" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="7" t="s">
+      <c r="A97" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C97" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D97" s="4" t="s">
+      <c r="C97" t="s">
+        <v>12</v>
+      </c>
+      <c r="D97" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="7" t="s">
+      <c r="A98" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C98" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D98" s="4" t="s">
+      <c r="C98" t="s">
+        <v>12</v>
+      </c>
+      <c r="D98" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="7" t="s">
+      <c r="A99" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C99" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D99" s="4" t="s">
+      <c r="C99" t="s">
+        <v>12</v>
+      </c>
+      <c r="D99" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="7" t="s">
+      <c r="A100" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C100" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D100" s="4" t="s">
+      <c r="C100" t="s">
+        <v>12</v>
+      </c>
+      <c r="D100" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="7" t="s">
+      <c r="A101" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C101" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D101" s="4" t="s">
+      <c r="C101" t="s">
+        <v>12</v>
+      </c>
+      <c r="D101" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="7" t="s">
+      <c r="A102" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C102" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D102" s="4" t="s">
+      <c r="C102" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="7" t="s">
+      <c r="A103" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C103" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D103" s="4" t="s">
+      <c r="C103" t="s">
+        <v>12</v>
+      </c>
+      <c r="D103" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="7" t="s">
+      <c r="A104" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C104" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D104" s="4" t="s">
+      <c r="C104" t="s">
+        <v>12</v>
+      </c>
+      <c r="D104" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="7" t="s">
+      <c r="A105" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C105" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D105" s="4" t="s">
+      <c r="C105" t="s">
+        <v>12</v>
+      </c>
+      <c r="D105" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="7" t="s">
+      <c r="A106" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C106" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D106" s="4" t="s">
+      <c r="C106" t="s">
+        <v>12</v>
+      </c>
+      <c r="D106" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="7" t="s">
+      <c r="A107" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C107" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D107" s="4" t="s">
+      <c r="C107" t="s">
+        <v>12</v>
+      </c>
+      <c r="D107" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="7" t="s">
+      <c r="A108" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C108" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D108" s="4" t="s">
+      <c r="C108" t="s">
+        <v>12</v>
+      </c>
+      <c r="D108" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="7" t="s">
+      <c r="A109" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C109" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D109" s="4" t="s">
+      <c r="C109" t="s">
+        <v>12</v>
+      </c>
+      <c r="D109" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="7" t="s">
+      <c r="A110" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C110" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D110" s="4" t="s">
+      <c r="C110" t="s">
+        <v>12</v>
+      </c>
+      <c r="D110" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="7" t="s">
+      <c r="A111" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="C111" t="s">
         <v>117</v>
       </c>
-      <c r="D111" s="4" t="s">
+      <c r="D111" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="7" t="s">
+      <c r="A112" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C112" t="s">
         <v>117</v>
       </c>
-      <c r="D112" s="4" t="s">
+      <c r="D112" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="7" t="s">
+      <c r="A113" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C113" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D113" s="4" t="s">
+      <c r="C113" t="s">
+        <v>12</v>
+      </c>
+      <c r="D113" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" s="7" t="s">
+      <c r="A114" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C114" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D114" s="4" t="s">
+      <c r="C114" t="s">
+        <v>12</v>
+      </c>
+      <c r="D114" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A115" s="7" t="s">
+      <c r="A115" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C115" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D115" s="4" t="s">
+      <c r="C115" t="s">
+        <v>12</v>
+      </c>
+      <c r="D115" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A116" s="7" t="s">
+      <c r="A116" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="C116" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D116" s="6" t="s">
+      <c r="C116" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D116" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="E116" s="6" t="s">
+      <c r="E116" s="5" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A117" s="7" t="s">
+      <c r="A117" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="C117" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D117" s="6" t="s">
+      <c r="C117" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D117" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="E117" s="6" t="s">
+      <c r="E117" s="5" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A118" s="7" t="s">
+      <c r="A118" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="C118" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D118" s="6" t="s">
+      <c r="C118" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D118" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="E118" s="6" t="s">
+      <c r="E118" s="5" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A119" s="7" t="s">
+      <c r="A119" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="C119" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D119" s="6" t="s">
+      <c r="C119" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D119" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="E119" s="6" t="s">
+      <c r="E119" s="5" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A120" s="7" t="s">
+      <c r="A120" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="C120" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D120" s="6" t="s">
+      <c r="C120" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D120" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="E120" s="6" t="s">
+      <c r="E120" s="5" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A121" s="7" t="s">
+      <c r="A121" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="C121" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D121" s="6" t="s">
+      <c r="C121" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D121" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="E121" s="6" t="s">
+      <c r="E121" s="5" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A122" s="7" t="s">
+      <c r="A122" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="C122" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D122" s="6" t="s">
+      <c r="C122" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D122" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="E122" s="6" t="s">
+      <c r="E122" s="5" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A123" s="7" t="s">
+      <c r="A123" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="C123" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D123" s="6" t="s">
+      <c r="C123" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D123" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="E123" s="6" t="s">
+      <c r="E123" s="5" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A124" s="7" t="s">
+      <c r="A124" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="C124" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D124" s="6" t="s">
+      <c r="C124" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D124" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="E124" s="6" t="s">
+      <c r="E124" s="5" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A125" s="7" t="s">
+      <c r="A125" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="C125" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D125" s="6" t="s">
+      <c r="C125" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D125" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E125" s="6" t="s">
+      <c r="E125" s="5" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A126" s="7" t="s">
+      <c r="A126" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C126" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D126" s="4" t="s">
+      <c r="C126" t="s">
+        <v>12</v>
+      </c>
+      <c r="D126" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A127" s="7" t="s">
+      <c r="A127" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C127" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D127" s="4" t="s">
+      <c r="C127" t="s">
+        <v>12</v>
+      </c>
+      <c r="D127" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A128" s="7" t="s">
+      <c r="A128" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C128" s="4" t="s">
+      <c r="C128" t="s">
         <v>85</v>
       </c>
-      <c r="D128" s="4" t="s">
+      <c r="D128" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A129" s="7" t="s">
+      <c r="A129" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C129" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D129" s="6" t="s">
+      <c r="C129" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D129" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="E129" s="6" t="s">
+      <c r="E129" s="5" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A130" s="7" t="s">
+      <c r="A130" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C130" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D130" s="6" t="s">
+      <c r="C130" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D130" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="E130" s="6" t="s">
+      <c r="E130" s="5" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A131" s="7" t="s">
+      <c r="A131" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C131" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D131" s="6" t="s">
+      <c r="C131" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D131" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="E131" s="6" t="s">
+      <c r="E131" s="5" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A132" s="7" t="s">
+      <c r="A132" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D132" s="6" t="s">
+      <c r="C132" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D132" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="E132" s="6" t="s">
+      <c r="E132" s="5" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A133" s="7" t="s">
+      <c r="A133" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D133" s="6" t="s">
+      <c r="C133" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D133" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="E133" s="6" t="s">
+      <c r="E133" s="5" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A134" s="7" t="s">
+      <c r="A134" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C134" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D134" s="6" t="s">
+      <c r="C134" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D134" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E134" s="6" t="s">
+      <c r="E134" s="5" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A135" s="7" t="s">
+      <c r="A135" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C135" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D135" s="6" t="s">
+      <c r="C135" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D135" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="E135" s="6" t="s">
+      <c r="E135" s="5" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A136" s="7" t="s">
+      <c r="A136" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C136" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D136" s="6" t="s">
+      <c r="C136" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D136" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="E136" s="6" t="s">
+      <c r="E136" s="5" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A137" s="7" t="s">
+      <c r="A137" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C137" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D137" s="6" t="s">
+      <c r="C137" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D137" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="E137" s="6" t="s">
+      <c r="E137" s="5" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A138" s="7" t="s">
+      <c r="A138" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C138" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D138" s="6" t="s">
+      <c r="C138" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D138" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="E138" s="6" t="s">
+      <c r="E138" s="5" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A139" s="7" t="s">
+      <c r="A139" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C139" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D139" s="6" t="s">
+      <c r="C139" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D139" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="E139" s="6" t="s">
+      <c r="E139" s="5" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A140" s="7" t="s">
+      <c r="A140" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C140" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D140" s="6" t="s">
+      <c r="C140" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D140" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="E140" s="6" t="s">
+      <c r="E140" s="5" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A141" s="7" t="s">
+      <c r="A141" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C141" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D141" s="6" t="s">
+      <c r="C141" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D141" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="E141" s="6" t="s">
+      <c r="E141" s="5" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A142" s="7" t="s">
+      <c r="A142" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C142" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D142" s="6" t="s">
+      <c r="C142" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D142" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="E142" s="6" t="s">
+      <c r="E142" s="5" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A143" s="7" t="s">
+      <c r="A143" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C143" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D143" s="6" t="s">
+      <c r="C143" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D143" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="E143" s="6" t="s">
+      <c r="E143" s="5" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A144" s="7" t="s">
+      <c r="A144" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C144" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D144" s="6" t="s">
+      <c r="C144" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D144" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="E144" s="6" t="s">
+      <c r="E144" s="5" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A145" s="7" t="s">
+      <c r="A145" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C145" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D145" s="6" t="s">
+      <c r="C145" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D145" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="E145" s="6" t="s">
+      <c r="E145" s="5" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A146" s="7" t="s">
+      <c r="A146" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C146" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D146" s="6" t="s">
+      <c r="C146" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D146" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="E146" s="6" t="s">
+      <c r="E146" s="5" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A147" s="7" t="s">
+      <c r="A147" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C147" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D147" s="6" t="s">
+      <c r="C147" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D147" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="E147" s="6" t="s">
+      <c r="E147" s="5" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A148" s="7" t="s">
+      <c r="A148" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C148" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D148" s="6" t="s">
+      <c r="C148" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D148" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="E148" s="6" t="s">
+      <c r="E148" s="5" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A149" s="7" t="s">
+      <c r="A149" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C149" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D149" s="6" t="s">
+      <c r="C149" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D149" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="E149" s="6" t="s">
+      <c r="E149" s="5" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A150" s="7" t="s">
+      <c r="A150" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C150" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D150" s="6" t="s">
+      <c r="C150" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D150" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="E150" s="6" t="s">
+      <c r="E150" s="5" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A151" s="7" t="s">
+      <c r="A151" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C151" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D151" s="6" t="s">
+      <c r="C151" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D151" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="E151" s="6" t="s">
+      <c r="E151" s="5" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A152" s="7" t="s">
+      <c r="A152" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C152" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D152" s="6" t="s">
+      <c r="C152" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D152" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="E152" s="6" t="s">
+      <c r="E152" s="5" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A153" s="7" t="s">
+      <c r="A153" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C153" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D153" s="6" t="s">
+      <c r="C153" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D153" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="E153" s="6" t="s">
+      <c r="E153" s="5" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A154" s="7" t="s">
+      <c r="A154" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C154" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D154" s="6" t="s">
+      <c r="C154" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D154" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="E154" s="6" t="s">
+      <c r="E154" s="5" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A155" s="7" t="s">
+      <c r="A155" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C155" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D155" s="6" t="s">
+      <c r="C155" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D155" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="E155" s="6" t="s">
+      <c r="E155" s="5" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A156" s="7" t="s">
+      <c r="A156" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C156" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D156" s="6" t="s">
+      <c r="C156" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D156" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="E156" s="6" t="s">
+      <c r="E156" s="5" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A157" s="7" t="s">
+      <c r="A157" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C157" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D157" s="6" t="s">
+      <c r="C157" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D157" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="E157" s="6" t="s">
+      <c r="E157" s="5" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A158" s="7" t="s">
+      <c r="A158" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C158" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D158" s="6" t="s">
+      <c r="C158" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D158" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="E158" s="6" t="s">
+      <c r="E158" s="5" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A159" s="7" t="s">
+      <c r="A159" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C159" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D159" s="6" t="s">
+      <c r="C159" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D159" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="E159" s="6" t="s">
+      <c r="E159" s="5" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A160" s="7" t="s">
+      <c r="A160" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C160" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D160" s="6" t="s">
+      <c r="C160" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D160" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="E160" s="6" t="s">
+      <c r="E160" s="5" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A161" s="7" t="s">
+      <c r="A161" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C161" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D161" s="6" t="s">
+      <c r="C161" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D161" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="E161" s="6" t="s">
+      <c r="E161" s="5" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A162" s="7" t="s">
+      <c r="A162" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C162" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D162" s="6" t="s">
+      <c r="C162" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D162" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="E162" s="6" t="s">
+      <c r="E162" s="5" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A163" s="7" t="s">
+      <c r="A163" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C163" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D163" s="6" t="s">
+      <c r="C163" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D163" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="E163" s="6" t="s">
+      <c r="E163" s="5" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A164" s="7" t="s">
+      <c r="A164" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C164" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D164" s="6" t="s">
+      <c r="C164" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D164" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="E164" s="6" t="s">
+      <c r="E164" s="5" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A165" s="7" t="s">
+      <c r="A165" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C165" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D165" s="6" t="s">
+      <c r="C165" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D165" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="E165" s="6" t="s">
+      <c r="E165" s="5" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A166" s="7" t="s">
+      <c r="A166" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C166" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D166" s="6" t="s">
+      <c r="C166" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D166" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="E166" s="6" t="s">
+      <c r="E166" s="5" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A167" s="7" t="s">
+      <c r="A167" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C167" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D167" s="6" t="s">
+      <c r="C167" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D167" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="E167" s="6" t="s">
+      <c r="E167" s="5" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A168" s="7" t="s">
+      <c r="A168" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C168" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D168" s="6" t="s">
+      <c r="C168" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D168" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="E168" s="6" t="s">
+      <c r="E168" s="5" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A169" s="7" t="s">
+      <c r="A169" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C169" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D169" s="6" t="s">
+      <c r="C169" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D169" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="E169" s="6" t="s">
+      <c r="E169" s="5" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A170" s="7" t="s">
+      <c r="A170" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C170" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D170" s="6" t="s">
+      <c r="C170" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D170" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="E170" s="6" t="s">
+      <c r="E170" s="5" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A171" s="7" t="s">
+      <c r="A171" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C171" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D171" s="6" t="s">
+      <c r="C171" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D171" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="E171" s="6" t="s">
+      <c r="E171" s="5" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A172" s="7" t="s">
+      <c r="A172" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C172" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D172" s="6" t="s">
+      <c r="C172" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D172" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="E172" s="6" t="s">
+      <c r="E172" s="5" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A173" s="7" t="s">
+      <c r="A173" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C173" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D173" s="6" t="s">
+      <c r="C173" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D173" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="E173" s="6" t="s">
+      <c r="E173" s="5" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A174" s="7" t="s">
+      <c r="A174" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C174" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D174" s="6" t="s">
+      <c r="C174" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D174" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="E174" s="6" t="s">
+      <c r="E174" s="5" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A175" s="7" t="s">
+      <c r="A175" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C175" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D175" s="6" t="s">
+      <c r="C175" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D175" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="E175" s="6" t="s">
+      <c r="E175" s="5" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A176" s="7" t="s">
+      <c r="A176" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C176" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D176" s="6" t="s">
+      <c r="C176" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D176" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="E176" s="6" t="s">
+      <c r="E176" s="5" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="177" spans="1:11" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A177" s="7" t="s">
+    <row r="177" spans="1:11" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A177" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B177" s="4"/>
-      <c r="C177" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D177" s="6" t="s">
+      <c r="B177"/>
+      <c r="C177" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D177" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="E177" s="6" t="s">
+      <c r="E177" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="F177" s="4"/>
-      <c r="G177" s="4"/>
-      <c r="H177" s="4"/>
-      <c r="I177" s="4"/>
-      <c r="J177" s="4"/>
-      <c r="K177" s="4"/>
-    </row>
-    <row r="178" spans="1:11" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A178" s="7" t="s">
+      <c r="F177"/>
+      <c r="G177"/>
+      <c r="H177"/>
+      <c r="I177"/>
+      <c r="J177"/>
+      <c r="K177"/>
+    </row>
+    <row r="178" spans="1:11" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A178" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B178" s="4"/>
-      <c r="C178" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D178" s="6" t="s">
+      <c r="B178"/>
+      <c r="C178" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D178" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="E178" s="6" t="s">
+      <c r="E178" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="F178" s="4"/>
-      <c r="G178" s="4"/>
-      <c r="H178" s="4"/>
-      <c r="I178" s="4"/>
-      <c r="J178" s="4"/>
-      <c r="K178" s="4"/>
+      <c r="F178"/>
+      <c r="G178"/>
+      <c r="H178"/>
+      <c r="I178"/>
+      <c r="J178"/>
+      <c r="K178"/>
     </row>
     <row r="179" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A179" s="7" t="s">
+      <c r="A179" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C179" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D179" s="6" t="s">
+      <c r="C179" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D179" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="E179" s="6" t="s">
+      <c r="E179" s="5" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="180" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A180" s="7" t="s">
+      <c r="A180" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C180" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D180" s="6" t="s">
+      <c r="C180" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D180" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="E180" s="6" t="s">
+      <c r="E180" s="5" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="181" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A181" s="7" t="s">
+      <c r="A181" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C181" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D181" s="6" t="s">
+      <c r="C181" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D181" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="E181" s="6" t="s">
+      <c r="E181" s="5" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A182" s="7" t="s">
+      <c r="A182" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C182" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D182" s="6" t="s">
+      <c r="C182" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D182" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="E182" s="6" t="s">
+      <c r="E182" s="5" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="183" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A183" s="7" t="s">
+      <c r="A183" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C183" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D183" s="6" t="s">
+      <c r="C183" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D183" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="E183" s="6" t="s">
+      <c r="E183" s="5" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="184" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A184" s="7" t="s">
+      <c r="A184" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C184" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D184" s="6" t="s">
+      <c r="C184" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D184" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="E184" s="6" t="s">
+      <c r="E184" s="5" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="185" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A185" s="7" t="s">
+      <c r="A185" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C185" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D185" s="6" t="s">
+      <c r="C185" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D185" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="E185" s="6" t="s">
+      <c r="E185" s="5" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A186" s="7" t="s">
+      <c r="A186" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C186" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D186" s="6" t="s">
+      <c r="C186" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D186" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="E186" s="6" t="s">
+      <c r="E186" s="5" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="187" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A187" s="7" t="s">
+      <c r="A187" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C187" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D187" s="6" t="s">
+      <c r="C187" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D187" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="E187" s="6" t="s">
+      <c r="E187" s="5" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="188" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A188" s="7" t="s">
+      <c r="A188" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C188" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D188" s="6" t="s">
+      <c r="C188" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D188" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="E188" s="6" t="s">
+      <c r="E188" s="5" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A189" s="7" t="s">
+      <c r="A189" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C189" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D189" s="6" t="s">
+      <c r="C189" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D189" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="E189" s="6" t="s">
+      <c r="E189" s="5" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="190" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A190" s="7" t="s">
+      <c r="A190" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C190" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D190" s="6" t="s">
+      <c r="C190" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D190" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="E190" s="6" t="s">
+      <c r="E190" s="5" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="191" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A191" s="7" t="s">
+      <c r="A191" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C191" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D191" s="6" t="s">
+      <c r="C191" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D191" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="E191" s="6" t="s">
+      <c r="E191" s="5" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="192" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A192" s="7" t="s">
+      <c r="A192" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C192" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D192" s="6" t="s">
+      <c r="C192" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D192" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="E192" s="6" t="s">
+      <c r="E192" s="5" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A193" s="7" t="s">
+      <c r="A193" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C193" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D193" s="6" t="s">
+      <c r="C193" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D193" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="E193" s="6" t="s">
+      <c r="E193" s="5" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="194" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A194" s="7" t="s">
+      <c r="A194" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C194" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D194" s="6" t="s">
+      <c r="C194" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D194" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="E194" s="6" t="s">
+      <c r="E194" s="5" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="195" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A195" s="7" t="s">
+      <c r="A195" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C195" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D195" s="6" t="s">
+      <c r="C195" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D195" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="E195" s="6" t="s">
+      <c r="E195" s="5" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A196" s="7" t="s">
+      <c r="A196" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C196" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D196" s="6" t="s">
+      <c r="C196" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D196" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="E196" s="6" t="s">
+      <c r="E196" s="5" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="197" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A197" s="7" t="s">
+      <c r="A197" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C197" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D197" s="6" t="s">
+      <c r="C197" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D197" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="E197" s="6" t="s">
+      <c r="E197" s="5" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A198" s="7" t="s">
+      <c r="A198" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="C198" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D198" s="6" t="s">
+      <c r="C198" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D198" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="E198" s="6" t="s">
+      <c r="E198" s="5" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A199" s="7" t="s">
+      <c r="A199" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="C199" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D199" s="6" t="s">
+      <c r="C199" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D199" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="E199" s="6" t="s">
+      <c r="E199" s="5" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A200" s="7" t="s">
+      <c r="A200" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="C200" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D200" s="6" t="s">
+      <c r="C200" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D200" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="E200" s="6" t="s">
+      <c r="E200" s="5" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A201" s="7" t="s">
+      <c r="A201" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C201" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D201" s="6" t="s">
+      <c r="C201" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D201" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="E201" s="6" t="s">
+      <c r="E201" s="5" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A202" s="7" t="s">
+      <c r="A202" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C202" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D202" s="4" t="s">
+      <c r="C202" t="s">
+        <v>12</v>
+      </c>
+      <c r="D202" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A203" s="7" t="s">
+      <c r="A203" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C203" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D203" s="4" t="s">
+      <c r="C203" t="s">
+        <v>12</v>
+      </c>
+      <c r="D203" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A204" s="7" t="s">
+      <c r="A204" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C204" s="4" t="s">
+      <c r="C204" t="s">
         <v>117</v>
       </c>
-      <c r="D204" s="4" t="s">
+      <c r="D204" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A205" s="4" t="s">
+      <c r="A205" t="s">
         <v>84</v>
       </c>
-      <c r="C205" s="4" t="s">
+      <c r="C205" t="s">
         <v>85</v>
       </c>
-      <c r="D205" s="4" t="s">
+      <c r="D205" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A206" s="4" t="s">
+      <c r="A206" t="s">
         <v>64</v>
       </c>
-      <c r="C206" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D206" s="4" t="s">
+      <c r="C206" t="s">
+        <v>12</v>
+      </c>
+      <c r="D206" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A207" s="4" t="s">
+      <c r="A207" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C207" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D207" s="4" t="s">
+      <c r="C207" t="s">
+        <v>12</v>
+      </c>
+      <c r="D207" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A208" s="4" t="s">
+      <c r="A208" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C208" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D208" s="4" t="s">
+      <c r="C208" t="s">
+        <v>12</v>
+      </c>
+      <c r="D208" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A209" s="4" t="s">
+      <c r="A209" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C209" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D209" s="4" t="s">
+      <c r="C209" t="s">
+        <v>12</v>
+      </c>
+      <c r="D209" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A210" s="4" t="s">
+      <c r="A210" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C210" s="4" t="s">
+      <c r="C210" t="s">
         <v>85</v>
       </c>
-      <c r="D210" s="4" t="s">
+      <c r="D210" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A211" s="4" t="s">
+      <c r="A211" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C211" s="4" t="s">
+      <c r="C211" t="s">
         <v>117</v>
       </c>
-      <c r="D211" s="4" t="s">
+      <c r="D211" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A212" s="4" t="s">
+      <c r="A212" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C212" s="4" t="s">
+      <c r="C212" t="s">
         <v>117</v>
       </c>
-      <c r="D212" s="4" t="s">
+      <c r="D212" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="213" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A213" s="10" t="s">
+      <c r="A213" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="B213" s="9"/>
-      <c r="C213" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="D213" s="10" t="s">
+      <c r="B213" s="7"/>
+      <c r="C213" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D213" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E213" s="10" t="s">
+      <c r="E213" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="F213" s="9"/>
-      <c r="G213" s="9" t="s">
+      <c r="F213" s="7"/>
+      <c r="G213" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="H213" s="9"/>
-      <c r="I213" s="9"/>
-      <c r="J213" s="9"/>
-      <c r="K213" s="9"/>
+      <c r="H213" s="7"/>
+      <c r="I213" s="7"/>
+      <c r="J213" s="7"/>
+      <c r="K213" s="7"/>
     </row>
     <row r="214" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A214" s="10" t="s">
+      <c r="A214" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="B214" s="9"/>
-      <c r="C214" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="D214" s="10" t="s">
+      <c r="B214" s="7"/>
+      <c r="C214" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D214" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="E214" s="10" t="s">
+      <c r="E214" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="F214" s="9"/>
-      <c r="G214" s="9"/>
-      <c r="H214" s="9"/>
-      <c r="I214" s="9"/>
-      <c r="J214" s="9"/>
-      <c r="K214" s="9"/>
+      <c r="F214" s="7"/>
+      <c r="G214" s="7"/>
+      <c r="H214" s="7"/>
+      <c r="I214" s="7"/>
+      <c r="J214" s="7"/>
+      <c r="K214" s="7"/>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A215" s="6" t="s">
+      <c r="A215" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C215" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D215" s="6" t="s">
+      <c r="C215" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D215" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E215" s="6" t="s">
+      <c r="E215" s="5" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A216" s="6" t="s">
+      <c r="A216" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C216" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D216" s="6" t="s">
+      <c r="C216" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D216" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="E216" s="6" t="s">
+      <c r="E216" s="5" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A217" s="6" t="s">
+      <c r="A217" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C217" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D217" s="6" t="s">
+      <c r="C217" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D217" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="E217" s="6" t="s">
+      <c r="E217" s="5" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A218" s="6" t="s">
+      <c r="A218" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C218" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D218" s="6" t="s">
+      <c r="C218" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D218" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="E218" s="6" t="s">
+      <c r="E218" s="5" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A219" s="6" t="s">
+      <c r="A219" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C219" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D219" s="6" t="s">
+      <c r="C219" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D219" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="E219" s="6" t="s">
+      <c r="E219" s="5" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A220" s="6" t="s">
+      <c r="A220" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C220" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D220" s="6" t="s">
+      <c r="C220" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D220" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="E220" s="6" t="s">
+      <c r="E220" s="5" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A221" s="6" t="s">
+      <c r="A221" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="C221" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D221" s="6" t="s">
+      <c r="C221" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D221" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="E221" s="6" t="s">
+      <c r="E221" s="5" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A222" s="6" t="s">
+      <c r="A222" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="C222" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D222" s="6" t="s">
+      <c r="C222" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D222" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="E222" s="6" t="s">
+      <c r="E222" s="5" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A223" s="6" t="s">
+      <c r="A223" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="C223" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D223" s="6" t="s">
+      <c r="C223" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D223" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="E223" s="6" t="s">
+      <c r="E223" s="5" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A224" s="6" t="s">
+      <c r="A224" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="C224" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D224" s="6" t="s">
+      <c r="C224" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D224" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="E224" s="6" t="s">
+      <c r="E224" s="5" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A225" s="6" t="s">
+      <c r="A225" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="C225" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D225" s="6" t="s">
+      <c r="C225" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D225" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="E225" s="6" t="s">
+      <c r="E225" s="5" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="226" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A226" s="6" t="s">
+      <c r="A226" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="C226" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D226" s="6" t="s">
+      <c r="C226" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D226" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E226" s="6" t="s">
+      <c r="E226" s="5" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A227" s="4" t="s">
+      <c r="A227" t="s">
         <v>133</v>
       </c>
-      <c r="C227" s="4" t="s">
+      <c r="C227" t="s">
         <v>117</v>
       </c>
-      <c r="D227" s="4" t="s">
+      <c r="D227" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A228" s="6" t="s">
+      <c r="A228" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="C228" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D228" s="6" t="s">
+      <c r="C228" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D228" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="E228" s="6" t="s">
+      <c r="E228" s="5" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A229" s="6" t="s">
+      <c r="A229" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="C229" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D229" s="6" t="s">
+      <c r="C229" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D229" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="E229" s="6" t="s">
+      <c r="E229" s="5" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A230" s="6" t="s">
+      <c r="A230" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="C230" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D230" s="6" t="s">
+      <c r="C230" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D230" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="E230" s="6" t="s">
+      <c r="E230" s="5" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A231" s="6" t="s">
+      <c r="A231" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="C231" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D231" s="6" t="s">
+      <c r="C231" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D231" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="E231" s="6" t="s">
+      <c r="E231" s="5" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A232" s="6" t="s">
+      <c r="A232" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="C232" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D232" s="6" t="s">
+      <c r="C232" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D232" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="E232" s="6" t="s">
+      <c r="E232" s="5" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A233" s="6" t="s">
+      <c r="A233" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="C233" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D233" s="6" t="s">
+      <c r="C233" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D233" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="E233" s="6" t="s">
+      <c r="E233" s="5" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A234" s="6" t="s">
+      <c r="A234" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="C234" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D234" s="6" t="s">
+      <c r="C234" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D234" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="E234" s="6" t="s">
+      <c r="E234" s="5" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A235" s="6" t="s">
+      <c r="A235" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="C235" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D235" s="6" t="s">
+      <c r="C235" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D235" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="E235" s="6" t="s">
+      <c r="E235" s="5" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A236" s="6" t="s">
+      <c r="A236" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="C236" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D236" s="6" t="s">
+      <c r="C236" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D236" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="E236" s="6" t="s">
+      <c r="E236" s="5" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A237" s="6" t="s">
+      <c r="A237" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="C237" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D237" s="6" t="s">
+      <c r="C237" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D237" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="E237" s="6" t="s">
+      <c r="E237" s="5" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A238" s="6" t="s">
+      <c r="A238" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="C238" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D238" s="6" t="s">
+      <c r="C238" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D238" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="E238" s="6" t="s">
+      <c r="E238" s="5" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A239" s="6" t="s">
+      <c r="A239" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="C239" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D239" s="6" t="s">
+      <c r="C239" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D239" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="E239" s="6" t="s">
+      <c r="E239" s="5" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A240" s="6" t="s">
+      <c r="A240" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="C240" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D240" s="6" t="s">
+      <c r="C240" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D240" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="E240" s="6" t="s">
+      <c r="E240" s="5" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A241" s="4" t="s">
+      <c r="A241" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C241" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D241" s="4" t="s">
+      <c r="C241" t="s">
+        <v>12</v>
+      </c>
+      <c r="D241" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A242" s="4" t="s">
+      <c r="A242" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C242" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D242" s="4" t="s">
+      <c r="C242" t="s">
+        <v>12</v>
+      </c>
+      <c r="D242" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A243" s="4" t="s">
+      <c r="A243" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C243" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D243" s="4" t="s">
+      <c r="C243" t="s">
+        <v>12</v>
+      </c>
+      <c r="D243" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A244" s="4" t="s">
+      <c r="A244" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C244" s="4" t="s">
+      <c r="C244" t="s">
         <v>117</v>
       </c>
-      <c r="D244" s="4" t="s">
+      <c r="D244" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A245" s="4" t="s">
+      <c r="A245" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C245" s="4" t="s">
+      <c r="C245" t="s">
         <v>117</v>
       </c>
-      <c r="D245" s="4" t="s">
+      <c r="D245" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A246" s="4" t="s">
+      <c r="A246" t="s">
         <v>145</v>
       </c>
-      <c r="C246" s="4" t="s">
+      <c r="C246" t="s">
         <v>117</v>
       </c>
-      <c r="D246" s="4" t="s">
+      <c r="D246" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A247" s="4" t="s">
+      <c r="A247" t="s">
         <v>145</v>
       </c>
-      <c r="C247" s="4" t="s">
+      <c r="C247" t="s">
         <v>117</v>
       </c>
-      <c r="D247" s="4" t="s">
+      <c r="D247" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A248" s="6" t="s">
+      <c r="A248" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="C248" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D248" s="6" t="s">
+      <c r="C248" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D248" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="E248" s="6" t="s">
+      <c r="E248" s="5" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A249" s="6" t="s">
+      <c r="A249" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="C249" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D249" s="6" t="s">
+      <c r="C249" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D249" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="E249" s="6" t="s">
+      <c r="E249" s="5" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A250" s="6" t="s">
+      <c r="A250" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="C250" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D250" s="6" t="s">
+      <c r="C250" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D250" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="E250" s="6" t="s">
+      <c r="E250" s="5" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A251" s="6" t="s">
+      <c r="A251" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="C251" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D251" s="6" t="s">
+      <c r="C251" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D251" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="E251" s="6" t="s">
+      <c r="E251" s="5" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A252" s="6" t="s">
+      <c r="A252" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="C252" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D252" s="6" t="s">
+      <c r="C252" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D252" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="E252" s="6" t="s">
+      <c r="E252" s="5" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A253" s="6" t="s">
+      <c r="A253" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="C253" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D253" s="6" t="s">
+      <c r="C253" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D253" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="E253" s="6" t="s">
+      <c r="E253" s="5" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A254" s="6" t="s">
+      <c r="A254" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="C254" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D254" s="6" t="s">
+      <c r="C254" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D254" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="E254" s="6" t="s">
+      <c r="E254" s="5" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A255" s="6" t="s">
+      <c r="A255" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="C255" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D255" s="6" t="s">
+      <c r="C255" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D255" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="E255" s="6" t="s">
+      <c r="E255" s="5" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A256" s="6" t="s">
+      <c r="A256" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="C256" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D256" s="6" t="s">
+      <c r="C256" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D256" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="E256" s="6" t="s">
+      <c r="E256" s="5" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A257" s="6" t="s">
+      <c r="A257" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="C257" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D257" s="6" t="s">
+      <c r="C257" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D257" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="E257" s="6" t="s">
+      <c r="E257" s="5" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A258" s="6" t="s">
+      <c r="A258" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="C258" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D258" s="6" t="s">
+      <c r="C258" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D258" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="E258" s="6" t="s">
+      <c r="E258" s="5" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A259" s="4" t="s">
+      <c r="A259" t="s">
         <v>80</v>
       </c>
-      <c r="C259" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D259" s="4" t="s">
+      <c r="C259" t="s">
+        <v>12</v>
+      </c>
+      <c r="D259" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A260" s="4" t="s">
+      <c r="A260" t="s">
         <v>80</v>
       </c>
-      <c r="C260" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D260" s="4" t="s">
+      <c r="C260" t="s">
+        <v>12</v>
+      </c>
+      <c r="D260" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A261" s="4" t="s">
+      <c r="A261" t="s">
         <v>80</v>
       </c>
-      <c r="C261" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D261" s="4" t="s">
+      <c r="C261" t="s">
+        <v>12</v>
+      </c>
+      <c r="D261" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A262" s="4" t="s">
+      <c r="A262" t="s">
         <v>80</v>
       </c>
-      <c r="C262" s="4" t="s">
+      <c r="C262" t="s">
         <v>108</v>
       </c>
-      <c r="D262" s="4" t="s">
+      <c r="D262" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A263" s="4" t="s">
+      <c r="A263" t="s">
         <v>80</v>
       </c>
-      <c r="C263" s="4" t="s">
+      <c r="C263" t="s">
         <v>108</v>
       </c>
-      <c r="D263" s="4" t="s">
+      <c r="D263" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A264" s="4" t="s">
+      <c r="A264" t="s">
         <v>80</v>
       </c>
-      <c r="C264" s="4" t="s">
+      <c r="C264" t="s">
         <v>117</v>
       </c>
-      <c r="D264" s="4" t="s">
+      <c r="D264" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A265" s="4" t="s">
+      <c r="A265" t="s">
         <v>80</v>
       </c>
-      <c r="C265" s="4" t="s">
+      <c r="C265" t="s">
         <v>117</v>
       </c>
-      <c r="D265" s="4" t="s">
+      <c r="D265" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A266" s="4" t="s">
+      <c r="A266" t="s">
         <v>65</v>
       </c>
-      <c r="C266" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D266" s="4" t="s">
+      <c r="C266" t="s">
+        <v>12</v>
+      </c>
+      <c r="D266" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A267" s="4" t="s">
+      <c r="A267" t="s">
         <v>65</v>
       </c>
-      <c r="C267" s="4" t="s">
+      <c r="C267" t="s">
         <v>117</v>
       </c>
-      <c r="D267" s="4" t="s">
+      <c r="D267" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A268" s="4" t="s">
+      <c r="A268" t="s">
         <v>65</v>
       </c>
-      <c r="C268" s="4" t="s">
+      <c r="C268" t="s">
         <v>117</v>
       </c>
-      <c r="D268" s="4" t="s">
+      <c r="D268" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A269" s="4" t="s">
+      <c r="A269" t="s">
         <v>146</v>
       </c>
-      <c r="C269" s="4" t="s">
+      <c r="C269" t="s">
         <v>117</v>
       </c>
-      <c r="D269" s="4" t="s">
+      <c r="D269" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A270" s="4" t="s">
+      <c r="A270" t="s">
         <v>146</v>
       </c>
-      <c r="C270" s="4" t="s">
+      <c r="C270" t="s">
         <v>117</v>
       </c>
-      <c r="D270" s="4" t="s">
+      <c r="D270" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A271" s="4" t="s">
+      <c r="A271" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C271" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D271" s="4" t="s">
+      <c r="C271" t="s">
+        <v>12</v>
+      </c>
+      <c r="D271" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A272" s="4" t="s">
+      <c r="A272" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C272" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D272" s="4" t="s">
+      <c r="C272" t="s">
+        <v>12</v>
+      </c>
+      <c r="D272" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A273" s="4" t="s">
+      <c r="A273" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C273" s="4" t="s">
+      <c r="C273" t="s">
         <v>117</v>
       </c>
-      <c r="D273" s="4" t="s">
+      <c r="D273" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A274" s="4" t="s">
+      <c r="A274" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C274" s="4" t="s">
+      <c r="C274" t="s">
         <v>117</v>
       </c>
-      <c r="D274" s="4" t="s">
+      <c r="D274" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A275" s="4" t="s">
+      <c r="A275" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C275" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D275" s="4" t="s">
+      <c r="C275" t="s">
+        <v>12</v>
+      </c>
+      <c r="D275" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A276" s="4" t="s">
+      <c r="A276" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C276" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D276" s="4" t="s">
+      <c r="C276" t="s">
+        <v>12</v>
+      </c>
+      <c r="D276" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A277" s="4" t="s">
+      <c r="A277" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C277" s="4" t="s">
+      <c r="C277" t="s">
         <v>117</v>
       </c>
-      <c r="D277" s="4" t="s">
+      <c r="D277" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A278" s="4" t="s">
+      <c r="A278" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C278" s="4" t="s">
+      <c r="C278" t="s">
         <v>117</v>
       </c>
-      <c r="D278" s="4" t="s">
+      <c r="D278" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A279" s="4" t="s">
+      <c r="A279" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C279" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D279" s="4" t="s">
+      <c r="C279" t="s">
+        <v>12</v>
+      </c>
+      <c r="D279" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A280" s="4" t="s">
+      <c r="A280" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C280" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D280" s="4" t="s">
+      <c r="C280" t="s">
+        <v>12</v>
+      </c>
+      <c r="D280" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A281" s="4" t="s">
+      <c r="A281" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C281" s="4" t="s">
+      <c r="C281" t="s">
         <v>117</v>
       </c>
-      <c r="D281" s="4" t="s">
+      <c r="D281" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A282" s="4" t="s">
+      <c r="A282" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C282" s="4" t="s">
+      <c r="C282" t="s">
         <v>117</v>
       </c>
-      <c r="D282" s="4" t="s">
+      <c r="D282" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A283" s="4" t="s">
+      <c r="A283" t="s">
         <v>70</v>
       </c>
-      <c r="C283" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D283" s="4" t="s">
+      <c r="C283" t="s">
+        <v>12</v>
+      </c>
+      <c r="D283" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A284" s="4" t="s">
+      <c r="A284" t="s">
         <v>70</v>
       </c>
-      <c r="C284" s="4" t="s">
+      <c r="C284" t="s">
         <v>117</v>
       </c>
-      <c r="D284" s="4" t="s">
+      <c r="D284" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A285" s="4" t="s">
+      <c r="A285" t="s">
         <v>138</v>
       </c>
-      <c r="C285" s="4" t="s">
+      <c r="C285" t="s">
         <v>117</v>
       </c>
-      <c r="D285" s="4" t="s">
+      <c r="D285" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A286" s="4" t="s">
+      <c r="A286" t="s">
         <v>138</v>
       </c>
-      <c r="C286" s="4" t="s">
+      <c r="C286" t="s">
         <v>117</v>
       </c>
-      <c r="D286" s="4" t="s">
+      <c r="D286" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A287" s="4" t="s">
+      <c r="A287" t="s">
         <v>138</v>
       </c>
-      <c r="C287" s="4" t="s">
+      <c r="C287" t="s">
         <v>117</v>
       </c>
-      <c r="D287" s="4" t="s">
+      <c r="D287" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A288" s="4" t="s">
+      <c r="A288" t="s">
         <v>138</v>
       </c>
-      <c r="C288" s="4" t="s">
+      <c r="C288" t="s">
         <v>117</v>
       </c>
-      <c r="D288" s="4" t="s">
+      <c r="D288" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A289" s="4" t="s">
+      <c r="A289" t="s">
         <v>141</v>
       </c>
-      <c r="C289" s="4" t="s">
+      <c r="C289" t="s">
         <v>117</v>
       </c>
-      <c r="D289" s="4" t="s">
+      <c r="D289" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A290" s="4" t="s">
+      <c r="A290" t="s">
         <v>79</v>
       </c>
-      <c r="C290" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D290" s="4" t="s">
+      <c r="C290" t="s">
+        <v>12</v>
+      </c>
+      <c r="D290" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A291" s="4" t="s">
+      <c r="A291" t="s">
         <v>79</v>
       </c>
-      <c r="C291" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D291" s="4" t="s">
+      <c r="C291" t="s">
+        <v>12</v>
+      </c>
+      <c r="D291" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A292" s="4" t="s">
+      <c r="A292" t="s">
         <v>75</v>
       </c>
-      <c r="C292" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D292" s="4" t="s">
+      <c r="C292" t="s">
+        <v>12</v>
+      </c>
+      <c r="D292" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A293" s="4" t="s">
+      <c r="A293" t="s">
         <v>75</v>
       </c>
-      <c r="C293" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D293" s="4" t="s">
+      <c r="C293" t="s">
+        <v>12</v>
+      </c>
+      <c r="D293" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A294" s="4" t="s">
+      <c r="A294" t="s">
         <v>76</v>
       </c>
-      <c r="C294" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D294" s="4" t="s">
+      <c r="C294" t="s">
+        <v>12</v>
+      </c>
+      <c r="D294" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A295" s="4" t="s">
+      <c r="A295" t="s">
         <v>76</v>
       </c>
-      <c r="C295" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D295" s="4" t="s">
+      <c r="C295" t="s">
+        <v>12</v>
+      </c>
+      <c r="D295" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A296" s="4" t="s">
+      <c r="A296" t="s">
         <v>77</v>
       </c>
-      <c r="C296" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D296" s="4" t="s">
+      <c r="C296" t="s">
+        <v>12</v>
+      </c>
+      <c r="D296" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A297" s="4" t="s">
+      <c r="A297" t="s">
         <v>77</v>
       </c>
-      <c r="C297" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D297" s="4" t="s">
+      <c r="C297" t="s">
+        <v>12</v>
+      </c>
+      <c r="D297" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A298" s="4" t="s">
+      <c r="A298" t="s">
         <v>77</v>
       </c>
-      <c r="C298" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D298" s="4" t="s">
+      <c r="C298" t="s">
+        <v>12</v>
+      </c>
+      <c r="D298" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A299" s="4" t="s">
+      <c r="A299" t="s">
         <v>144</v>
       </c>
-      <c r="C299" s="4" t="s">
+      <c r="C299" t="s">
         <v>117</v>
       </c>
-      <c r="D299" s="4" t="s">
+      <c r="D299" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A300" s="4" t="s">
+      <c r="A300" t="s">
         <v>144</v>
       </c>
-      <c r="C300" s="4" t="s">
+      <c r="C300" t="s">
         <v>117</v>
       </c>
-      <c r="D300" s="4" t="s">
+      <c r="D300" t="s">
         <v>132</v>
       </c>
     </row>
